--- a/scripts/templates/church_data_import_template.xlsx
+++ b/scripts/templates/church_data_import_template.xlsx
@@ -14,6 +14,7 @@
     <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Groups (Tier 2)" sheetId="5" state="visible" r:id="rId5"/>
     <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Departments" sheetId="6" state="visible" r:id="rId6"/>
     <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Members" sheetId="7" state="visible" r:id="rId7"/>
+    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Consent &amp; Accuracy" sheetId="8" state="visible" r:id="rId8"/>
   </sheets>
   <definedNames/>
   <calcPr calcId="124519" fullCalcOnLoad="1"/>
@@ -23,7 +24,7 @@
 <file path=xl/styles.xml><?xml version="1.0" encoding="utf-8"?>
 <styleSheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
   <numFmts count="0"/>
-  <fonts count="7">
+  <fonts count="8">
     <font>
       <name val="Calibri"/>
       <family val="2"/>
@@ -58,6 +59,11 @@
       <color rgb="009890C4"/>
       <sz val="10"/>
     </font>
+    <font>
+      <b val="1"/>
+      <color rgb="003C3489"/>
+      <sz val="11"/>
+    </font>
   </fonts>
   <fills count="3">
     <fill>
@@ -72,7 +78,7 @@
       </patternFill>
     </fill>
   </fills>
-  <borders count="2">
+  <borders count="3">
     <border>
       <left/>
       <right/>
@@ -94,11 +100,16 @@
         <color rgb="00DDDAF5"/>
       </bottom>
     </border>
+    <border>
+      <bottom style="thin">
+        <color rgb="00534AB7"/>
+      </bottom>
+    </border>
   </borders>
   <cellStyleXfs count="1">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0"/>
   </cellStyleXfs>
-  <cellXfs count="8">
+  <cellXfs count="11">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
     <xf numFmtId="0" fontId="1" fillId="0" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
     <xf numFmtId="0" fontId="2" fillId="0" borderId="0" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
@@ -113,6 +124,11 @@
     <xf numFmtId="0" fontId="0" fillId="0" borderId="1" pivotButton="0" quotePrefix="0" xfId="0"/>
     <xf numFmtId="0" fontId="5" fillId="0" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
     <xf numFmtId="0" fontId="6" fillId="0" borderId="1" pivotButton="0" quotePrefix="0" xfId="0"/>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="0" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <alignment vertical="top" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="7" fillId="0" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="2" pivotButton="0" quotePrefix="0" xfId="0"/>
   </cellXfs>
   <cellStyles count="1">
     <cellStyle name="Normal" xfId="0" builtinId="0" hidden="0"/>
@@ -478,7 +494,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:A14"/>
+  <dimension ref="A1:A15"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="100" customWidth="1" min="1" max="1"/>
@@ -546,23 +562,30 @@
         </is>
       </c>
     </row>
-    <row r="11" ht="18" customHeight="1">
-      <c r="A11" s="2" t="inlineStr"/>
-    </row>
-    <row r="12" ht="34" customHeight="1">
-      <c r="A12" s="3" t="inlineStr">
+    <row r="11" ht="34" customHeight="1">
+      <c r="A11" s="2" t="inlineStr">
+        <is>
+          <t xml:space="preserve">  6. Fill in the "Consent &amp; Accuracy" sheet — this is required before we can import your data.</t>
+        </is>
+      </c>
+    </row>
+    <row r="12" ht="18" customHeight="1">
+      <c r="A12" s="2" t="inlineStr"/>
+    </row>
+    <row r="13" ht="34" customHeight="1">
+      <c r="A13" s="3" t="inlineStr">
         <is>
           <t>Do not rename the column headers or reorder the sheets — the import script matches by header name and sheet name.</t>
         </is>
       </c>
     </row>
-    <row r="13" ht="18" customHeight="1">
-      <c r="A13" s="2" t="inlineStr"/>
-    </row>
-    <row r="14" ht="34" customHeight="1">
-      <c r="A14" s="2" t="inlineStr">
-        <is>
-          <t>When you are done, send the completed file back the same way you received it. Whoever reviews and submits this file on your church’s behalf will be asked to confirm it has been reviewed for accuracy before it is imported — see the note on that screen for what that confirms.</t>
+    <row r="14" ht="18" customHeight="1">
+      <c r="A14" s="2" t="inlineStr"/>
+    </row>
+    <row r="15" ht="34" customHeight="1">
+      <c r="A15" s="2" t="inlineStr">
+        <is>
+          <t>When you are done, email the completed file to support@justshephrd.com. Do not upload it anywhere — there is no upload page for this; a SHEP.HERD team member imports it on your behalf once it arrives and the Consent &amp; Accuracy sheet is filled in.</t>
         </is>
       </c>
     </row>
@@ -1183,4 +1206,102 @@
   </mergeCells>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>
+</file>
+
+<file path=xl/worksheets/sheet8.xml><?xml version="1.0" encoding="utf-8"?>
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
+  <sheetPr>
+    <outlinePr summaryBelow="1" summaryRight="1"/>
+    <pageSetUpPr/>
+  </sheetPr>
+  <dimension ref="A1:B13"/>
+  <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
+  <cols>
+    <col width="100" customWidth="1" min="1" max="1"/>
+    <col width="40" customWidth="1" min="2" max="2"/>
+  </cols>
+  <sheetData>
+    <row r="1">
+      <c r="A1" s="1" t="inlineStr">
+        <is>
+          <t>Consent &amp; Data Accuracy</t>
+        </is>
+      </c>
+    </row>
+    <row r="2" ht="18" customHeight="1">
+      <c r="A2" s="8" t="inlineStr"/>
+    </row>
+    <row r="3" ht="34" customHeight="1">
+      <c r="A3" s="8" t="inlineStr">
+        <is>
+          <t>By completing and returning this file to SHEP.HERD, the person named below confirms, on behalf of the church, that:</t>
+        </is>
+      </c>
+    </row>
+    <row r="4" ht="34" customHeight="1">
+      <c r="A4" s="8" t="inlineStr">
+        <is>
+          <t xml:space="preserve">  • The information in this file has been reviewed for accuracy by someone with authority to do so.</t>
+        </is>
+      </c>
+    </row>
+    <row r="5" ht="34" customHeight="1">
+      <c r="A5" s="8" t="inlineStr">
+        <is>
+          <t xml:space="preserve">  • SHEP.HERD is not responsible for errors, omissions, or outdated information contained in the data provided in this file — the church remains responsible for the accuracy of its own records.</t>
+        </is>
+      </c>
+    </row>
+    <row r="6" ht="34" customHeight="1">
+      <c r="A6" s="8" t="inlineStr">
+        <is>
+          <t xml:space="preserve">  • SHEP.HERD will import this data as provided, and the church can correct any entry afterward from within the app.</t>
+        </is>
+      </c>
+    </row>
+    <row r="7" ht="18" customHeight="1">
+      <c r="A7" s="8" t="inlineStr"/>
+    </row>
+    <row r="8" ht="18" customHeight="1">
+      <c r="A8" s="8" t="inlineStr">
+        <is>
+          <t>Please fill in and return with the completed sheets:</t>
+        </is>
+      </c>
+    </row>
+    <row r="10">
+      <c r="A10" s="9" t="inlineStr">
+        <is>
+          <t>Full Name</t>
+        </is>
+      </c>
+      <c r="B10" s="10" t="inlineStr"/>
+    </row>
+    <row r="11">
+      <c r="A11" s="9" t="inlineStr">
+        <is>
+          <t>Title / Role at Church</t>
+        </is>
+      </c>
+      <c r="B11" s="10" t="inlineStr"/>
+    </row>
+    <row r="12">
+      <c r="A12" s="9" t="inlineStr">
+        <is>
+          <t>Church Name</t>
+        </is>
+      </c>
+      <c r="B12" s="10" t="inlineStr"/>
+    </row>
+    <row r="13">
+      <c r="A13" s="9" t="inlineStr">
+        <is>
+          <t>Date</t>
+        </is>
+      </c>
+      <c r="B13" s="10" t="inlineStr"/>
+    </row>
+  </sheetData>
+  <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
+</worksheet>
 </file>